--- a/hrm/.plans/elearning-hoc-vien/trang-chu/testcase.xlsx
+++ b/hrm/.plans/elearning-hoc-vien/trang-chu/testcase.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nút 'Xem tất cả' của 4 nhóm điều hướng thật; các nút banner/danh mục/vinh danh chỉ demo toast.</t>
+          <t>Nút 'Xem tất cả' của 4 nhóm + Danh mục điều hướng thật; click danh mục/hoạt động gần đây/CTA carousel mở chi tiết tương ứng.</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>NHIỀU nút là DEMO (chỉ toast 'Demo: ...', không điều hướng): 'Bạn cần học', 'Khuyến nghị', 'Xem' hoạt động, 'Xem tất cả' của Danh mục, click CategoryCard, click Vinh danh. Chuỗi 'Bảng vàng tháng 01' hardcode.</t>
+          <t>Nửa trái banner là HeroCarousel (tự chạy 6s, có CTA điều hướng thật). 'Hoạt động gần đây' + 'Danh mục nội dung' + CTA carousel đều điều hướng thật tới chi tiết/danh sách. Vinh danh dùng dữ liệu thật, thẻ KHÔNG click, ẩn khi admin tắt.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -1220,7 +1220,7 @@
       <c r="B22" s="11" t="n"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>II. NÚT DEMO (CHỈ TOAST)</t>
+          <t>II. HERO CAROUSEL (MỚI)</t>
         </is>
       </c>
       <c r="D22" s="4" t="n"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>NÚT DEMO (CHỈ TOAST)</t>
+          <t>HERO CAROUSEL (MỚI)</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -1254,22 +1254,22 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Nút 'Bạn cần học' trên banner</t>
+          <t>Carousel tự chạy</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Ở trang chủ</t>
+          <t>Có ≥2 slide (cần học/khuyến nghị/nổi bật)</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>1. Bấm 'Bạn cần học' trên banner</t>
+          <t>1. Vào trang chủ, quan sát HeroCarousel ~6s</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>- Toast 'Demo: Bạn cần học' (KHÔNG điều hướng)</t>
+          <t>- Slide tự chuyển sau ~6s; dot indicator đổi theo</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>Hành vi demo</t>
+          <t>BR-05</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NÚT DEMO (CHỈ TOAST)</t>
+          <t>HERO CAROUSEL (MỚI)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Nút 'Khuyến nghị' trên banner</t>
+          <t>Chuyển slide thủ công</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Ở trang chủ</t>
+          <t>Có ≥2 slide</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1. Bấm 'Khuyến nghị' trên banner</t>
+          <t>1. Bấm nút › (hoặc dot / phím →)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>- Toast 'Demo: Khuyến nghị'</t>
+          <t>- Chuyển sang slide kế; đồng hồ tự chạy nạp lại</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Hành vi demo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>NÚT DEMO (CHỈ TOAST)</t>
+          <t>HERO CAROUSEL (MỚI)</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Nút 'Xem' hoạt động gần đây</t>
+          <t>Tạm dừng khi hover / nút pause</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Ở trang chủ</t>
+          <t>Có ≥2 slide</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>1. Bấm 'Xem' ở panel hoạt động</t>
+          <t>1. Rê chuột vào slide (hoặc bấm nút pause)</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>- Toast 'Demo: Xem tất cả hoạt động'</t>
+          <t>- Carousel dừng tự chuyển; rời chuột/bấm play → chạy lại</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>Hành vi demo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NÚT DEMO (CHỈ TOAST)</t>
+          <t>HERO CAROUSEL (MỚI)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1461,22 +1461,22 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>'Xem tất cả' Danh mục</t>
+          <t>Bấm CTA vào học</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Ở trang chủ</t>
+          <t>Slide là khóa đang học</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1. Bấm 'Xem tất cả' ở 'Danh mục nội dung'</t>
+          <t>1. Bấm nút CTA (VD 'Học tiếp 40%')</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>- Toast 'Demo: Danh mục'</t>
+          <t>- Mở chi tiết khóa/lộ trình tương ứng</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Hành vi demo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>NÚT DEMO (CHỈ TOAST)</t>
+          <t>HERO CAROUSEL (MỚI)</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Click danh mục</t>
+          <t>Slide fallback khi rỗng</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Có danh mục</t>
+          <t>Không có dữ liệu gợi ý</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>1. Click 1 thẻ danh mục</t>
+          <t>1. Vào trang chủ</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>- Toast 'Demo: mở danh mục {tên}'</t>
+          <t>- Hiện 1 slide 'Học theo khoá • Theo dõi rõ', KHÔNG có CTA, KHÔNG click được</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>Hành vi demo</t>
+          <t>BR-05</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr"/>
@@ -1581,95 +1581,95 @@
       </c>
       <c r="O27" s="14" t="inlineStr"/>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>II. DANH MỤC &amp; HOẠT ĐỘNG GẦN ĐÂY (ĐIỀU HƯỚNG THẬT)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Trang chủ</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>NÚT DEMO (CHỈ TOAST)</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>TC_02.006</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Click thẻ Vinh danh</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Có vinh danh</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>1. Click 1 thẻ vinh danh</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>- Toast 'Demo: mở vinh danh {tên}'</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Hành vi demo</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>III. ĐIỀU HƯỚNG THẬT</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="5" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>DANH MỤC &amp; HOẠT ĐỘNG GẦN ĐÂY (ĐIỀU HƯỚNG THẬT)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>TC_02.001</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Xem tất cả Danh mục nội dung</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Ở trang chủ</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm 'Xem tất cả' ở 'Danh mục nội dung'</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>- Mở /hoc-theo-loai-dao-tao (danh sách khóa)</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>BR-03</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
@@ -1679,17 +1679,17 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>ĐIỀU HƯỚNG THẬT</t>
+          <t>DANH MỤC &amp; HOẠT ĐỘNG GẦN ĐÂY (ĐIỀU HƯỚNG THẬT)</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>TC_03.001</t>
+          <t>TC_02.002</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Xem tất cả 'Bạn cần học'</t>
+          <t>Click 1 danh mục</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>Nhóm có dữ liệu</t>
+          <t>Có danh mục</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>1. Bấm 'Xem tất cả' ở 'Bạn cần học'</t>
+          <t>1. Click 1 thẻ CategoryCard</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>- Mở trang /noi-dung/bat-buoc (danh sách đầy đủ)</t>
+          <t>- Mở danh sách khóa lọc theo loại đó (/hoc-theo-loai-dao-tao?training_type_id=...)</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>BR-03</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr"/>
@@ -1748,17 +1748,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ĐIỀU HƯỚNG THẬT</t>
+          <t>DANH MỤC &amp; HOẠT ĐỘNG GẦN ĐÂY (ĐIỀU HƯỚNG THẬT)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>TC_03.002</t>
+          <t>TC_02.003</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Xem tất cả 'Nội dung mới'</t>
+          <t>Click 1 hoạt động gần đây</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Nhóm có dữ liệu</t>
+          <t>Có hoạt động có slug</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1. Bấm 'Xem tất cả' ở 'Nội dung mới'</t>
+          <t>1. Click 1 dòng trong 'Hoạt động gần đây'</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>- Mở /noi-dung/moi</t>
+          <t>- Mở chi tiết khóa/lộ trình tương ứng</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BR-04</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
@@ -1817,32 +1817,32 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>ĐIỀU HƯỚNG THẬT</t>
+          <t>DANH MỤC &amp; HOẠT ĐỘNG GẦN ĐÂY (ĐIỀU HƯỚNG THẬT)</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>TC_03.003</t>
+          <t>TC_02.004</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Click thẻ khóa học</t>
+          <t>Hoạt động gần đây rỗng</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Có thẻ loại 'Khoá học'</t>
+          <t>Chưa có hoạt động</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>1. Click 1 thẻ 'Khoá học'/'Môn học'</t>
+          <t>1. Xem panel 'Hoạt động gần đây'</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>- Mở chi tiết khóa (/khoa-hoc/:slug)</t>
+          <t>- Hiện 'Chưa có hoạt động nào'</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>BR-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr"/>
@@ -1878,95 +1878,95 @@
       </c>
       <c r="O32" s="14" t="inlineStr"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>II. VINH DANH (DỮ LIỆU THẬT)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Trang chủ</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>ĐIỀU HƯỚNG THẬT</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>TC_03.004</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Click thẻ lộ trình</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Có thẻ loại 'Lộ trình'</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1. Click 1 thẻ 'Lộ trình'</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>- Mở chi tiết lộ trình (/lo-trinh/:slug)</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>BR-02</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>IV. TRANG XEM TẤT CẢ (/noi-dung/:type)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="5" t="n"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>VINH DANH (DỮ LIỆU THẬT)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>TC_02.001</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Vinh danh hiển thị dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Admin bật khối + có học viên vinh danh</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>1. Cuộn tới 'Vinh danh học viên'</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>- Hiện thẻ thật (avatar, tên, phòng ban, thành tích); thẻ KHÔNG click được</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>BR-06</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
@@ -1976,148 +1976,607 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
+          <t>VINH DANH (DỮ LIỆU THẬT)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>TC_02.002</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Ẩn khối khi admin tắt</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Admin tắt khối vinh danh (is_enabled=0)</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>1. Vào trang chủ</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>- Khối 'Vinh danh học viên' KHÔNG hiển thị</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>BR-06</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr"/>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N35" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>VINH DANH (DỮ LIỆU THẬT)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>TC_02.003</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Marquee cuộn khi &gt;3 thẻ</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Có &gt;3 học viên vinh danh</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>1. Quan sát khối vinh danh, rê chuột vào</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>- Thẻ tự cuộn ngang; hover → dừng cuộn</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>III. ĐIỀU HƯỚNG THẬT</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>ĐIỀU HƯỚNG THẬT</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>TC_03.001</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Xem tất cả 'Bạn cần học'</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Nhóm có dữ liệu</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>1. Bấm 'Xem tất cả' ở 'Bạn cần học'</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>- Mở trang /noi-dung/bat-buoc (danh sách đầy đủ)</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>BR-01</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr"/>
+      <c r="L38" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>ĐIỀU HƯỚNG THẬT</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>TC_03.002</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Xem tất cả 'Nội dung mới'</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Nhóm có dữ liệu</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm 'Xem tất cả' ở 'Nội dung mới'</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>- Mở /noi-dung/moi</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>ĐIỀU HƯỚNG THẬT</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>TC_03.003</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Click thẻ khóa học</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Có thẻ loại 'Khoá học'</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>1. Click 1 thẻ 'Khoá học'/'Môn học'</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>- Mở chi tiết khóa (/khoa-hoc/:slug)</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>BR-02</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ĐIỀU HƯỚNG THẬT</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>TC_03.004</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Click thẻ lộ trình</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Có thẻ loại 'Lộ trình'</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>1. Click 1 thẻ 'Lộ trình'</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>- Mở chi tiết lộ trình (/lo-trinh/:slug)</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>BR-02</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>IV. TRANG XEM TẤT CẢ (/noi-dung/:type)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Trang chủ</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
           <t>TRANG XEM TẤT CẢ (/noi-dung/:type)</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>TC_04.001</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>Xem thêm nối danh sách</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>Nhóm có &gt; 12 mục</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>1. Vào /noi-dung/pho-bien
 2. Bấm 'Xem thêm'</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>- Nối thêm 12 mục; dòng 'Đã hiển thị {n} / {total} nội dung'</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>BR-04</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr"/>
-      <c r="L35" s="14" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M35" s="14" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N35" s="14" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O35" s="14" t="inlineStr"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="K43" s="14" t="inlineStr"/>
+      <c r="L43" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M43" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N43" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Trang chủ</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>TRANG XEM TẤT CẢ (/noi-dung/:type)</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>TC_04.002</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Slug sai → mặc định</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>1. Vào /noi-dung/khong-hop-le</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>- Mặc định về 'Nội dung mới'</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="28">
     <mergeCell ref="B4:O4"/>
     <mergeCell ref="B7:O7"/>
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="L11:O11"/>
+    <mergeCell ref="C28:O28"/>
+    <mergeCell ref="C37:O37"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="C18:O18"/>
-    <mergeCell ref="C34:O34"/>
+    <mergeCell ref="C33:O33"/>
+    <mergeCell ref="C42:O42"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="B8:O8"/>
     <mergeCell ref="L13:O13"/>
@@ -2125,7 +2584,6 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="L12:O12"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="C29:O29"/>
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I15:K15"/>
@@ -2137,7 +2595,7 @@
     <mergeCell ref="B5:O5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L18:N137" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L18:N145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Pending,Not Executed"</formula1>
     </dataValidation>
   </dataValidations>
